--- a/DataTables/SupplierResults.xlsx
+++ b/DataTables/SupplierResults.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
   <si>
     <t>Sname</t>
   </si>
@@ -207,7 +207,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,11 +238,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -307,7 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -318,7 +313,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -832,9 +826,6 @@
       <c r="I7" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="J7" t="s" s="10">
-        <v>57</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/DataTables/SupplierResults.xlsx
+++ b/DataTables/SupplierResults.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="58">
   <si>
     <t>Sname</t>
   </si>
@@ -207,7 +207,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +238,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -302,7 +307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -313,6 +318,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -826,6 +832,9 @@
       <c r="I7" t="s" s="0">
         <v>18</v>
       </c>
+      <c r="J7" t="s" s="10">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
